--- a/data/amcare_silver_sample_data.xlsx
+++ b/data/amcare_silver_sample_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ptabl-my.sharepoint.com/personal/salma_audryani_abl_co_id/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project DS+AI\sia-engine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{35981F7C-90D0-4476-8AD2-8B29E31305B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABA2EE39-1F1C-4283-93E7-9DE9293E5960}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD23DC0-2DD1-460B-9335-97EDA0815C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-10740" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5360" yWindow="980" windowWidth="14390" windowHeight="6440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
@@ -846,12 +846,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -866,10 +872,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,42 +1217,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU21"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.9140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.08203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="54.296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="107.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" customWidth="1"/>
+    <col min="19" max="19" width="53.33203125" customWidth="1"/>
+    <col min="20" max="20" width="15.25" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="89.09765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.59765625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.69921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="38.3984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="43.19921875" customWidth="1"/>
-    <col min="37" max="37" width="48" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="44.8984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="31.59765625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="40.4140625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.58203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.08203125" customWidth="1"/>
+    <col min="32" max="32" width="8.6640625" style="3"/>
+    <col min="35" max="35" width="43.1640625" customWidth="1"/>
+    <col min="36" max="36" width="8.6640625" style="3"/>
+    <col min="37" max="37" width="9.58203125" style="3" customWidth="1"/>
+    <col min="38" max="38" width="9.1640625" style="3" customWidth="1"/>
+    <col min="39" max="39" width="15.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="31.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.6640625" style="3"/>
+    <col min="43" max="43" width="26.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="14.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1290,10 +1300,10 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
@@ -1311,7 +1321,7 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="X1" t="s">
@@ -1338,7 +1348,7 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" t="s">
@@ -1350,34 +1360,34 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
       <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AT1" t="s">
@@ -1387,8 +1397,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="1">
@@ -1421,10 +1431,10 @@
       <c r="M2" t="s">
         <v>51</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>53</v>
       </c>
       <c r="R2" t="s">
@@ -1442,7 +1452,7 @@
       <c r="V2" t="s">
         <v>58</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="3" t="s">
         <v>59</v>
       </c>
       <c r="Y2" t="s">
@@ -1466,7 +1476,7 @@
       <c r="AE2" t="s">
         <v>63</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG2" t="s">
@@ -1478,34 +1488,34 @@
       <c r="AI2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>72</v>
       </c>
       <c r="AP2" t="s">
         <v>73</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>76</v>
       </c>
       <c r="AT2">
@@ -1515,8 +1525,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B3" s="1">
@@ -1549,10 +1559,10 @@
       <c r="M3" t="s">
         <v>50</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>82</v>
       </c>
       <c r="R3" t="s">
@@ -1570,7 +1580,7 @@
       <c r="V3" t="s">
         <v>58</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="3" t="s">
         <v>86</v>
       </c>
       <c r="Y3" t="s">
@@ -1594,7 +1604,7 @@
       <c r="AE3" t="s">
         <v>63</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG3" t="s">
@@ -1606,34 +1616,34 @@
       <c r="AI3" t="s">
         <v>90</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AK3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AM3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AN3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AO3" s="3" t="s">
         <v>72</v>
       </c>
       <c r="AP3" t="s">
         <v>73</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AQ3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AS3" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT3">
@@ -1643,8 +1653,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B4" s="1">
@@ -1677,10 +1687,10 @@
       <c r="M4" t="s">
         <v>51</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>100</v>
       </c>
       <c r="R4" t="s">
@@ -1698,7 +1708,7 @@
       <c r="V4" t="s">
         <v>58</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="3" t="s">
         <v>104</v>
       </c>
       <c r="Y4" t="s">
@@ -1722,7 +1732,7 @@
       <c r="AE4" t="s">
         <v>63</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG4" t="s">
@@ -1734,34 +1744,34 @@
       <c r="AI4" t="s">
         <v>106</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AK4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AL4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AM4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AN4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AO4" s="3" t="s">
         <v>110</v>
       </c>
       <c r="AP4" t="s">
         <v>73</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AQ4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AR4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AS4" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT4">
@@ -1771,8 +1781,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B5" s="1">
@@ -1805,10 +1815,10 @@
       <c r="M5" t="s">
         <v>50</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="3" t="s">
         <v>116</v>
       </c>
       <c r="R5" t="s">
@@ -1826,7 +1836,7 @@
       <c r="V5" t="s">
         <v>58</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="3" t="s">
         <v>118</v>
       </c>
       <c r="Y5" t="s">
@@ -1850,7 +1860,7 @@
       <c r="AE5" t="s">
         <v>63</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AF5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG5" t="s">
@@ -1862,34 +1872,34 @@
       <c r="AI5" t="s">
         <v>121</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AJ5" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AK5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AL5" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AM5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AN5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AO5" s="3" t="s">
         <v>72</v>
       </c>
       <c r="AP5" t="s">
         <v>73</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AQ5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AR5" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AS5" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AT5">
@@ -1899,8 +1909,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B6" s="1">
@@ -1933,10 +1943,10 @@
       <c r="M6" t="s">
         <v>50</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="3" t="s">
         <v>116</v>
       </c>
       <c r="R6" t="s">
@@ -1954,7 +1964,7 @@
       <c r="V6" t="s">
         <v>58</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="3" t="s">
         <v>132</v>
       </c>
       <c r="Y6" t="s">
@@ -1978,7 +1988,7 @@
       <c r="AE6" t="s">
         <v>63</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AF6" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG6" t="s">
@@ -1990,34 +2000,34 @@
       <c r="AI6" t="s">
         <v>134</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AJ6" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AK6" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AL6" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AM6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AN6" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AO6" s="3" t="s">
         <v>110</v>
       </c>
       <c r="AP6" t="s">
         <v>73</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AQ6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AR6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AS6" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT6">
@@ -2027,8 +2037,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>137</v>
       </c>
       <c r="B7" s="1">
@@ -2061,10 +2071,10 @@
       <c r="M7" t="s">
         <v>140</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="3" t="s">
         <v>142</v>
       </c>
       <c r="R7" t="s">
@@ -2082,7 +2092,7 @@
       <c r="V7" t="s">
         <v>58</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W7" s="3" t="s">
         <v>146</v>
       </c>
       <c r="Y7" t="s">
@@ -2106,7 +2116,7 @@
       <c r="AE7" t="s">
         <v>63</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AF7" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG7" t="s">
@@ -2118,34 +2128,34 @@
       <c r="AI7" t="s">
         <v>149</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AJ7" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AK7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AL7" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AM7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AN7" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AO7" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP7" t="s">
         <v>73</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AQ7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AR7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AS7" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT7">
@@ -2155,8 +2165,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B8" s="1">
@@ -2189,10 +2199,10 @@
       <c r="M8" t="s">
         <v>51</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="Q8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="R8" t="s">
@@ -2210,7 +2220,7 @@
       <c r="V8" t="s">
         <v>58</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="3" t="s">
         <v>158</v>
       </c>
       <c r="Y8" t="s">
@@ -2234,7 +2244,7 @@
       <c r="AE8" t="s">
         <v>63</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AF8" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG8" t="s">
@@ -2246,34 +2256,34 @@
       <c r="AI8" t="s">
         <v>160</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AK8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AL8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AM8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AN8" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AO8" s="3" t="s">
         <v>110</v>
       </c>
       <c r="AP8" t="s">
         <v>73</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AQ8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AR8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="AS8" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT8">
@@ -2283,8 +2293,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>161</v>
       </c>
       <c r="B9" s="1">
@@ -2317,10 +2327,10 @@
       <c r="M9" t="s">
         <v>50</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" s="3" t="s">
         <v>82</v>
       </c>
       <c r="R9" t="s">
@@ -2338,7 +2348,7 @@
       <c r="V9" t="s">
         <v>58</v>
       </c>
-      <c r="W9" t="s">
+      <c r="W9" s="3" t="s">
         <v>166</v>
       </c>
       <c r="Y9" t="s">
@@ -2362,7 +2372,7 @@
       <c r="AE9" t="s">
         <v>63</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AF9" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG9" t="s">
@@ -2374,34 +2384,34 @@
       <c r="AI9" t="s">
         <v>168</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AK9" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AL9" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AM9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="AN9" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AO9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="AP9" t="s">
         <v>73</v>
       </c>
-      <c r="AQ9" t="s">
+      <c r="AQ9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AR9" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AS9" t="s">
+      <c r="AS9" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AT9">
@@ -2411,8 +2421,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B10" s="1">
@@ -2445,10 +2455,10 @@
       <c r="M10" t="s">
         <v>50</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="3" t="s">
         <v>176</v>
       </c>
       <c r="R10" t="s">
@@ -2466,7 +2476,7 @@
       <c r="V10" t="s">
         <v>58</v>
       </c>
-      <c r="W10" t="s">
+      <c r="W10" s="3" t="s">
         <v>179</v>
       </c>
       <c r="Y10" t="s">
@@ -2490,7 +2500,7 @@
       <c r="AE10" t="s">
         <v>63</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AF10" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG10" t="s">
@@ -2502,34 +2512,34 @@
       <c r="AI10" t="s">
         <v>182</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AJ10" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AK10" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AL10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM10" t="s">
+      <c r="AM10" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN10" t="s">
+      <c r="AN10" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO10" t="s">
+      <c r="AO10" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP10" t="s">
         <v>73</v>
       </c>
-      <c r="AQ10" t="s">
+      <c r="AQ10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR10" t="s">
+      <c r="AR10" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AS10" t="s">
+      <c r="AS10" s="3" t="s">
         <v>184</v>
       </c>
       <c r="AT10">
@@ -2539,8 +2549,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B11" s="1">
@@ -2573,10 +2583,10 @@
       <c r="M11" t="s">
         <v>50</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="3" t="s">
         <v>53</v>
       </c>
       <c r="R11" t="s">
@@ -2594,7 +2604,7 @@
       <c r="V11" t="s">
         <v>58</v>
       </c>
-      <c r="W11" t="s">
+      <c r="W11" s="3" t="s">
         <v>189</v>
       </c>
       <c r="Y11" t="s">
@@ -2618,7 +2628,7 @@
       <c r="AE11" t="s">
         <v>63</v>
       </c>
-      <c r="AF11" t="s">
+      <c r="AF11" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG11" t="s">
@@ -2630,34 +2640,34 @@
       <c r="AI11" t="s">
         <v>191</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AJ11" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AK11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AL11" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM11" t="s">
+      <c r="AM11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN11" t="s">
+      <c r="AN11" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO11" t="s">
+      <c r="AO11" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP11" t="s">
         <v>73</v>
       </c>
-      <c r="AQ11" t="s">
+      <c r="AQ11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AR11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS11" t="s">
+      <c r="AS11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT11">
@@ -2667,8 +2677,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B12" s="1">
@@ -2701,10 +2711,10 @@
       <c r="M12" t="s">
         <v>51</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q12" s="3" t="s">
         <v>195</v>
       </c>
       <c r="R12" t="s">
@@ -2722,7 +2732,7 @@
       <c r="V12" t="s">
         <v>58</v>
       </c>
-      <c r="W12" t="s">
+      <c r="W12" s="3" t="s">
         <v>196</v>
       </c>
       <c r="Y12" t="s">
@@ -2746,7 +2756,7 @@
       <c r="AE12" t="s">
         <v>63</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AF12" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG12" t="s">
@@ -2758,34 +2768,34 @@
       <c r="AI12" t="s">
         <v>198</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AJ12" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AK12" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AL12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AM12" t="s">
+      <c r="AM12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AN12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AO12" t="s">
+      <c r="AO12" s="3" t="s">
         <v>72</v>
       </c>
       <c r="AP12" t="s">
         <v>73</v>
       </c>
-      <c r="AQ12" t="s">
+      <c r="AQ12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR12" t="s">
+      <c r="AR12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS12" t="s">
+      <c r="AS12" s="3" t="s">
         <v>76</v>
       </c>
       <c r="AT12">
@@ -2795,8 +2805,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>200</v>
       </c>
       <c r="B13" s="1">
@@ -2829,10 +2839,10 @@
       <c r="M13" t="s">
         <v>51</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="Q13" s="3" t="s">
         <v>201</v>
       </c>
       <c r="R13" t="s">
@@ -2850,7 +2860,7 @@
       <c r="V13" t="s">
         <v>58</v>
       </c>
-      <c r="W13" t="s">
+      <c r="W13" s="3" t="s">
         <v>104</v>
       </c>
       <c r="Y13" t="s">
@@ -2874,7 +2884,7 @@
       <c r="AE13" t="s">
         <v>63</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AF13" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG13" t="s">
@@ -2886,34 +2896,34 @@
       <c r="AI13" t="s">
         <v>203</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AJ13" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AK13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AL13" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="AM13" t="s">
+      <c r="AM13" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN13" t="s">
+      <c r="AN13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO13" t="s">
+      <c r="AO13" s="3" t="s">
         <v>110</v>
       </c>
       <c r="AP13" t="s">
         <v>73</v>
       </c>
-      <c r="AQ13" t="s">
+      <c r="AQ13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR13" t="s">
+      <c r="AR13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS13" t="s">
+      <c r="AS13" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT13">
@@ -2923,8 +2933,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B14" s="1">
@@ -2957,10 +2967,10 @@
       <c r="M14" t="s">
         <v>50</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="Q14" s="3" t="s">
         <v>176</v>
       </c>
       <c r="R14" t="s">
@@ -2978,7 +2988,7 @@
       <c r="V14" t="s">
         <v>58</v>
       </c>
-      <c r="W14" t="s">
+      <c r="W14" s="3" t="s">
         <v>206</v>
       </c>
       <c r="Y14" t="s">
@@ -3002,7 +3012,7 @@
       <c r="AE14" t="s">
         <v>63</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AF14" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG14" t="s">
@@ -3014,34 +3024,34 @@
       <c r="AI14" t="s">
         <v>208</v>
       </c>
-      <c r="AJ14" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AK14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AL14" t="s">
+      <c r="AL14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AM14" t="s">
+      <c r="AM14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN14" t="s">
+      <c r="AN14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AO14" t="s">
+      <c r="AO14" s="3" t="s">
         <v>72</v>
       </c>
       <c r="AP14" t="s">
         <v>73</v>
       </c>
-      <c r="AQ14" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR14" t="s">
+      <c r="AR14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AS14" t="s">
+      <c r="AS14" s="3" t="s">
         <v>184</v>
       </c>
       <c r="AT14">
@@ -3051,8 +3061,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>210</v>
       </c>
       <c r="B15" s="1">
@@ -3085,10 +3095,10 @@
       <c r="M15" t="s">
         <v>50</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="Q15" s="3" t="s">
         <v>100</v>
       </c>
       <c r="R15" t="s">
@@ -3106,7 +3116,7 @@
       <c r="V15" t="s">
         <v>58</v>
       </c>
-      <c r="W15" t="s">
+      <c r="W15" s="3" t="s">
         <v>216</v>
       </c>
       <c r="Y15" t="s">
@@ -3130,7 +3140,7 @@
       <c r="AE15" t="s">
         <v>63</v>
       </c>
-      <c r="AF15" t="s">
+      <c r="AF15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG15" t="s">
@@ -3142,34 +3152,34 @@
       <c r="AI15" t="s">
         <v>218</v>
       </c>
-      <c r="AJ15" t="s">
+      <c r="AJ15" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AK15" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL15" t="s">
+      <c r="AL15" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM15" t="s">
+      <c r="AM15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN15" t="s">
+      <c r="AN15" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO15" t="s">
+      <c r="AO15" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP15" t="s">
         <v>73</v>
       </c>
-      <c r="AQ15" t="s">
+      <c r="AQ15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR15" t="s">
+      <c r="AR15" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AS15" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AT15">
@@ -3179,8 +3189,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B16" s="1">
@@ -3213,10 +3223,10 @@
       <c r="M16" t="s">
         <v>51</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q16" s="3" t="s">
         <v>142</v>
       </c>
       <c r="R16" t="s">
@@ -3234,7 +3244,7 @@
       <c r="V16" t="s">
         <v>58</v>
       </c>
-      <c r="W16" t="s">
+      <c r="W16" s="3" t="s">
         <v>223</v>
       </c>
       <c r="Y16" t="s">
@@ -3258,7 +3268,7 @@
       <c r="AE16" t="s">
         <v>63</v>
       </c>
-      <c r="AF16" t="s">
+      <c r="AF16" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG16" t="s">
@@ -3270,34 +3280,34 @@
       <c r="AI16" t="s">
         <v>225</v>
       </c>
-      <c r="AJ16" t="s">
+      <c r="AJ16" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="AK16" t="s">
+      <c r="AK16" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AL16" t="s">
+      <c r="AL16" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="AM16" t="s">
+      <c r="AM16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN16" t="s">
+      <c r="AN16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO16" t="s">
+      <c r="AO16" s="3" t="s">
         <v>110</v>
       </c>
       <c r="AP16" t="s">
         <v>73</v>
       </c>
-      <c r="AQ16" t="s">
+      <c r="AQ16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR16" t="s">
+      <c r="AR16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS16" t="s">
+      <c r="AS16" s="3" t="s">
         <v>76</v>
       </c>
       <c r="AT16">
@@ -3307,8 +3317,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>228</v>
       </c>
       <c r="B17" s="1">
@@ -3341,10 +3351,10 @@
       <c r="M17" t="s">
         <v>50</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="R17" t="s">
@@ -3362,7 +3372,7 @@
       <c r="V17" t="s">
         <v>58</v>
       </c>
-      <c r="W17" t="s">
+      <c r="W17" s="3" t="s">
         <v>231</v>
       </c>
       <c r="Y17" t="s">
@@ -3386,7 +3396,7 @@
       <c r="AE17" t="s">
         <v>63</v>
       </c>
-      <c r="AF17" t="s">
+      <c r="AF17" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG17" t="s">
@@ -3398,34 +3408,34 @@
       <c r="AI17" t="s">
         <v>234</v>
       </c>
-      <c r="AJ17" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="AK17" t="s">
+      <c r="AK17" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL17" t="s">
+      <c r="AL17" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM17" t="s">
+      <c r="AM17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN17" t="s">
+      <c r="AN17" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO17" t="s">
+      <c r="AO17" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP17" t="s">
         <v>73</v>
       </c>
-      <c r="AQ17" t="s">
+      <c r="AQ17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR17" t="s">
+      <c r="AR17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS17" t="s">
+      <c r="AS17" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT17">
@@ -3435,8 +3445,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>236</v>
       </c>
       <c r="B18" s="1">
@@ -3469,10 +3479,10 @@
       <c r="M18" t="s">
         <v>80</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q18" s="3" t="s">
         <v>239</v>
       </c>
       <c r="R18" t="s">
@@ -3490,7 +3500,7 @@
       <c r="V18" t="s">
         <v>58</v>
       </c>
-      <c r="W18" t="s">
+      <c r="W18" s="3" t="s">
         <v>241</v>
       </c>
       <c r="Y18" t="s">
@@ -3514,7 +3524,7 @@
       <c r="AE18" t="s">
         <v>63</v>
       </c>
-      <c r="AF18" t="s">
+      <c r="AF18" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG18" t="s">
@@ -3526,34 +3536,34 @@
       <c r="AI18" t="s">
         <v>244</v>
       </c>
-      <c r="AJ18" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="AK18" t="s">
+      <c r="AK18" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AL18" t="s">
+      <c r="AL18" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="AM18" t="s">
+      <c r="AM18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN18" t="s">
+      <c r="AN18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO18" t="s">
+      <c r="AO18" s="3" t="s">
         <v>247</v>
       </c>
       <c r="AP18" t="s">
         <v>73</v>
       </c>
-      <c r="AQ18" t="s">
+      <c r="AQ18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR18" t="s">
+      <c r="AR18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS18" t="s">
+      <c r="AS18" s="3" t="s">
         <v>76</v>
       </c>
       <c r="AT18">
@@ -3563,8 +3573,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>248</v>
       </c>
       <c r="B19" s="1">
@@ -3597,10 +3607,10 @@
       <c r="M19" t="s">
         <v>50</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q19" s="3" t="s">
         <v>252</v>
       </c>
       <c r="R19" t="s">
@@ -3618,7 +3628,7 @@
       <c r="V19" t="s">
         <v>58</v>
       </c>
-      <c r="W19" t="s">
+      <c r="W19" s="3" t="s">
         <v>254</v>
       </c>
       <c r="Y19" t="s">
@@ -3642,7 +3652,7 @@
       <c r="AE19" t="s">
         <v>63</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AF19" s="3" t="s">
         <v>64</v>
       </c>
       <c r="AG19" t="s">
@@ -3654,34 +3664,34 @@
       <c r="AI19" t="s">
         <v>256</v>
       </c>
-      <c r="AJ19" t="s">
+      <c r="AJ19" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="AK19" t="s">
+      <c r="AK19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL19" t="s">
+      <c r="AL19" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM19" t="s">
+      <c r="AM19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN19" t="s">
+      <c r="AN19" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO19" t="s">
+      <c r="AO19" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP19" t="s">
         <v>73</v>
       </c>
-      <c r="AQ19" t="s">
+      <c r="AQ19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="AR19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS19" t="s">
+      <c r="AS19" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT19">
@@ -3691,8 +3701,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B20" s="1">
@@ -3725,10 +3735,10 @@
       <c r="M20" t="s">
         <v>50</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q20" s="3" t="s">
         <v>100</v>
       </c>
       <c r="R20" t="s">
@@ -3746,7 +3756,7 @@
       <c r="V20" t="s">
         <v>58</v>
       </c>
-      <c r="W20" t="s">
+      <c r="W20" s="3" t="s">
         <v>260</v>
       </c>
       <c r="Y20" t="s">
@@ -3770,7 +3780,7 @@
       <c r="AE20" t="s">
         <v>63</v>
       </c>
-      <c r="AF20" t="s">
+      <c r="AF20" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG20" t="s">
@@ -3782,34 +3792,34 @@
       <c r="AI20" t="s">
         <v>262</v>
       </c>
-      <c r="AJ20" t="s">
+      <c r="AJ20" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="AK20" t="s">
+      <c r="AK20" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL20" t="s">
+      <c r="AL20" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AM20" t="s">
+      <c r="AM20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN20" t="s">
+      <c r="AN20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AO20" t="s">
+      <c r="AO20" s="3" t="s">
         <v>154</v>
       </c>
       <c r="AP20" t="s">
         <v>73</v>
       </c>
-      <c r="AQ20" t="s">
+      <c r="AQ20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR20" t="s">
+      <c r="AR20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AS20" t="s">
+      <c r="AS20" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AT20">
@@ -3819,8 +3829,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B21" s="1">
@@ -3853,10 +3863,10 @@
       <c r="M21" t="s">
         <v>50</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q21" s="3" t="s">
         <v>201</v>
       </c>
       <c r="R21" t="s">
@@ -3874,7 +3884,7 @@
       <c r="V21" t="s">
         <v>58</v>
       </c>
-      <c r="W21" t="s">
+      <c r="W21" s="3" t="s">
         <v>265</v>
       </c>
       <c r="Y21" t="s">
@@ -3898,7 +3908,7 @@
       <c r="AE21" t="s">
         <v>63</v>
       </c>
-      <c r="AF21" t="s">
+      <c r="AF21" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AG21" t="s">
@@ -3910,34 +3920,34 @@
       <c r="AI21" t="s">
         <v>267</v>
       </c>
-      <c r="AJ21" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="AK21" t="s">
+      <c r="AK21" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AL21" t="s">
+      <c r="AL21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AM21" t="s">
+      <c r="AM21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AN21" t="s">
+      <c r="AN21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO21" t="s">
+      <c r="AO21" s="3" t="s">
         <v>110</v>
       </c>
       <c r="AP21" t="s">
         <v>73</v>
       </c>
-      <c r="AQ21" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AR21" t="s">
+      <c r="AR21" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AS21" t="s">
+      <c r="AS21" s="3" t="s">
         <v>184</v>
       </c>
       <c r="AT21">
